--- a/xls/square_16_quad4_21.xlsx
+++ b/xls/square_16_quad4_21.xlsx
@@ -456,6 +456,76 @@
         <v>10</v>
       </c>
     </row>
+    <row r="19" spans="1:11">
+      <c r="A19" t="s">
+        <v>11</v>
+      </c>
+      <c r="B19">
+        <v>484</v>
+      </c>
+      <c r="C19" t="s">
+        <v>11</v>
+      </c>
+      <c r="D19">
+        <v>289</v>
+      </c>
+      <c r="E19" t="s">
+        <v>12</v>
+      </c>
+      <c r="F19">
+        <v>400</v>
+      </c>
+      <c r="G19" t="s">
+        <v>13</v>
+      </c>
+      <c r="H19">
+        <v>1083</v>
+      </c>
+      <c r="I19">
+        <v>-0.5679033449622201</v>
+      </c>
+      <c r="J19">
+        <v>-1.3946047741434333</v>
+      </c>
+      <c r="K19">
+        <v>1.9717731708424358</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11">
+      <c r="A20" t="s">
+        <v>11</v>
+      </c>
+      <c r="B20">
+        <v>484</v>
+      </c>
+      <c r="C20" t="s">
+        <v>11</v>
+      </c>
+      <c r="D20">
+        <v>289</v>
+      </c>
+      <c r="E20" t="s">
+        <v>12</v>
+      </c>
+      <c r="F20">
+        <v>441</v>
+      </c>
+      <c r="G20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H20">
+        <v>1200</v>
+      </c>
+      <c r="I20">
+        <v>-0.8972739277558719</v>
+      </c>
+      <c r="J20">
+        <v>-1.5336519222385159</v>
+      </c>
+      <c r="K20">
+        <v>1.8694421128189127</v>
+      </c>
+    </row>
     <row r="21" spans="1:11">
       <c r="A21" t="s">
         <v>11</v>
@@ -482,13 +552,13 @@
         <v>1323</v>
       </c>
       <c r="I21">
-        <v>-1.1848448392930755</v>
+        <v>-1.2839233925700804</v>
       </c>
       <c r="J21">
-        <v>-1.8134936888232507</v>
+        <v>-1.385814706672794</v>
       </c>
       <c r="K21">
-        <v>1.3285446232513378</v>
+        <v>2.0810852615506183</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -517,13 +587,13 @@
         <v>1452</v>
       </c>
       <c r="I22">
-        <v>-1.7339370374054073</v>
+        <v>-1.2083290364011852</v>
       </c>
       <c r="J22">
-        <v>-1.7084877733890687</v>
+        <v>-1.2752847057627397</v>
       </c>
       <c r="K22">
-        <v>1.705219171928332</v>
+        <v>4.109395104650417</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -552,13 +622,13 @@
         <v>1587</v>
       </c>
       <c r="I23">
-        <v>-1.5986076332518377</v>
+        <v>-1.4510511003556221</v>
       </c>
       <c r="J23">
-        <v>-1.5797322770363882</v>
+        <v>-1.2695987330701317</v>
       </c>
       <c r="K23">
-        <v>2.0820683804496327</v>
+        <v>4.485124943774613</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -587,13 +657,13 @@
         <v>1728</v>
       </c>
       <c r="I24">
-        <v>-1.5615557035853784</v>
+        <v>-0.3155169347997427</v>
       </c>
       <c r="J24">
-        <v>-1.3656269806345047</v>
+        <v>-0.2587648150390381</v>
       </c>
       <c r="K24">
-        <v>3.1894178510758553</v>
+        <v>4.85477340317326</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -622,13 +692,13 @@
         <v>1875</v>
       </c>
       <c r="I25">
-        <v>-0.8097517405224811</v>
+        <v>-0.014498355934567907</v>
       </c>
       <c r="J25">
-        <v>-0.5193432787207491</v>
+        <v>-0.012494591540949338</v>
       </c>
       <c r="K25">
-        <v>3.5169384414504137</v>
+        <v>4.416508563194563</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -657,13 +727,13 @@
         <v>2028</v>
       </c>
       <c r="I26">
-        <v>-0.00547582062549161</v>
+        <v>-3.891527608998145e-5</v>
       </c>
       <c r="J26">
-        <v>-0.005141212355903083</v>
+        <v>-3.73312679977729e-5</v>
       </c>
       <c r="K26">
-        <v>3.284188572501146</v>
+        <v>3.2404986431107954</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -692,13 +762,13 @@
         <v>2187</v>
       </c>
       <c r="I27">
-        <v>-0.008335014851083226</v>
+        <v>-5.3698633345857374e-5</v>
       </c>
       <c r="J27">
-        <v>-0.007992908975849432</v>
+        <v>-5.217842458754562e-5</v>
       </c>
       <c r="K27">
-        <v>3.3510908122404213</v>
+        <v>3.298453979903358</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -727,13 +797,13 @@
         <v>2352</v>
       </c>
       <c r="I28">
-        <v>-0.005005853452878617</v>
+        <v>-2.7579877466377425e-5</v>
       </c>
       <c r="J28">
-        <v>-0.005040244342700258</v>
+        <v>-2.7900561477253655e-5</v>
       </c>
       <c r="K28">
-        <v>3.304254460363916</v>
+        <v>3.157811624490545</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -762,13 +832,13 @@
         <v>2523</v>
       </c>
       <c r="I29">
-        <v>-0.0008153337091044505</v>
+        <v>-1.0514327249974985e-5</v>
       </c>
       <c r="J29">
-        <v>-0.0009446980832847359</v>
+        <v>-1.1608223287526049e-5</v>
       </c>
       <c r="K29">
-        <v>2.9944822463682454</v>
+        <v>3.008785244665648</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -797,13 +867,13 @@
         <v>2700</v>
       </c>
       <c r="I30">
-        <v>-0.0006613614131013417</v>
+        <v>-4.188492480386573e-6</v>
       </c>
       <c r="J30">
-        <v>-0.0007451965968773623</v>
+        <v>-4.488128928036265e-6</v>
       </c>
       <c r="K30">
-        <v>2.943004298469363</v>
+        <v>2.7591043633456773</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -832,13 +902,13 @@
         <v>2883</v>
       </c>
       <c r="I31">
-        <v>-0.0001220405458113373</v>
+        <v>-1.8237399265453577e-6</v>
       </c>
       <c r="J31">
-        <v>-0.0001552451419992641</v>
+        <v>-2.0415839390507016e-6</v>
       </c>
       <c r="K31">
-        <v>2.6332796955609825</v>
+        <v>2.6272686756117447</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -867,13 +937,13 @@
         <v>3072</v>
       </c>
       <c r="I32">
-        <v>-0.000271884396684127</v>
+        <v>-2.5837225314586303e-6</v>
       </c>
       <c r="J32">
-        <v>-0.0003211712854859778</v>
+        <v>-2.777101599018972e-6</v>
       </c>
       <c r="K32">
-        <v>2.761132617822953</v>
+        <v>2.6628752646171314</v>
       </c>
     </row>
   </sheetData>
